--- a/public/downloads/loan-amortization.xlsx
+++ b/public/downloads/loan-amortization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Explore Excel\Explore Excel Updated\explore-excel-complete\explore-excel\public\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63085438-9594-47B9-A22B-FB22E2B3C2A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2EC18A-432C-4708-BA79-C04E7E9CF3DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,11 +286,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3545,7 +3545,7 @@
         <v/>
       </c>
       <c r="F111" s="12" t="str">
-        <f t="shared" ref="F111:F142" si="15">IF(C111="","",C111+D111+E111)</f>
+        <f t="shared" ref="F111:F134" si="15">IF(C111="","",C111+D111+E111)</f>
         <v/>
       </c>
       <c r="G111" s="12" t="str">
@@ -3562,7 +3562,7 @@
         <v/>
       </c>
       <c r="C112" s="15" t="str">
-        <f t="shared" ref="C112:C143" si="16">IF(OR(G111="",N(G111)&lt;=0),"",MIN(N(G111),ROUND($C$10-D112,2)))</f>
+        <f t="shared" ref="C112:C134" si="16">IF(OR(G111="",N(G111)&lt;=0),"",MIN(N(G111),ROUND($C$10-D112,2)))</f>
         <v/>
       </c>
       <c r="D112" s="15" t="str">
@@ -4253,84 +4253,84 @@
       <c r="C2" s="17"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
     </row>
     <row r="5" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="21" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
     </row>
     <row r="8" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
     </row>
-    <row r="11" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="21" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
     </row>
-    <row r="14" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
     </row>
-    <row r="17" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="21" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
     </row>
     <row r="20" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="20"/>
@@ -4338,20 +4338,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
